--- a/Dataset_Nutrients_EmysOrbicularis_Meyer.xlsx
+++ b/Dataset_Nutrients_EmysOrbicularis_Meyer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magda\Documents\Code and data Emys#1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sumpfschildkroeten\Nutrients\final\Code and Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EC0E744-5FA7-49E7-A03E-41263247F42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49028EF8-DEF0-4584-B646-8B26B84FC608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A0B6A291-3840-436E-8046-6B380FD2FED0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A0B6A291-3840-436E-8046-6B380FD2FED0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="108">
   <si>
+    <t>SLBEZ</t>
+  </si>
+  <si>
     <t>sample_type</t>
   </si>
   <si>
@@ -358,9 +361,6 @@
   </si>
   <si>
     <t>Witzelsdorfer Rückstaudamm</t>
-  </si>
-  <si>
-    <t>sample_ID</t>
   </si>
 </sst>
 </file>
@@ -439,9 +439,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -479,7 +479,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -585,7 +585,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -727,7 +727,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -736,178 +736,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201ABDAB-DD7A-4C8E-894B-6F5866F73FEE}">
   <dimension ref="A1:AQ52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AP1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2">
         <v>0.46</v>
@@ -1000,45 +1000,45 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3" s="2">
         <v>0.3</v>
@@ -1131,45 +1131,45 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N4" s="2">
         <v>0.33</v>
@@ -1262,45 +1262,45 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N5" s="2">
         <v>0.39</v>
@@ -1393,45 +1393,45 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N6" s="2">
         <v>0.3</v>
@@ -1524,45 +1524,45 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N7" s="2">
         <v>0.67</v>
@@ -1655,45 +1655,45 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="2">
         <v>0.3</v>
@@ -1786,45 +1786,45 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9" s="2">
         <v>0.38</v>
@@ -1917,45 +1917,45 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N10" s="2">
         <v>0.33</v>
@@ -2048,45 +2048,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" s="2">
         <v>0.32</v>
@@ -2179,45 +2179,45 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" s="2">
         <v>0.63</v>
@@ -2310,45 +2310,45 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N13" s="2">
         <v>0.28000000000000003</v>
@@ -2441,45 +2441,45 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N14" s="2">
         <v>0.39</v>
@@ -2572,45 +2572,45 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2">
         <v>0.33</v>
@@ -2703,45 +2703,45 @@
         <v>1.6300000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N16" s="2">
         <v>0.6</v>
@@ -2834,18 +2834,18 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="3">
         <v>10</v>
@@ -2965,18 +2965,18 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
         <v>67</v>
       </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3">
         <v>11</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="4">
         <v>2</v>
@@ -3096,18 +3096,18 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1">
         <v>10</v>
@@ -3227,18 +3227,18 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3">
         <v>10.5</v>
@@ -3358,18 +3358,18 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E21" s="3">
         <v>10</v>
@@ -3489,18 +3489,18 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E22" s="1">
         <v>11</v>
@@ -3620,18 +3620,18 @@
         <v>1.6400000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" s="3">
         <v>12</v>
@@ -3751,18 +3751,18 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1">
         <v>11</v>
@@ -3882,18 +3882,18 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E25" s="3">
         <v>6</v>
@@ -4013,18 +4013,18 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" s="3">
         <v>12</v>
@@ -4144,18 +4144,18 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" s="3">
         <v>11</v>
@@ -4275,18 +4275,18 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3">
         <v>11</v>
@@ -4406,18 +4406,18 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" s="3">
         <v>12</v>
@@ -4537,18 +4537,18 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E30" s="3">
         <v>11</v>
@@ -4668,18 +4668,18 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E31" s="3">
         <v>10</v>
@@ -4799,18 +4799,18 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E32" s="3">
         <v>12</v>
@@ -4930,18 +4930,18 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E33" s="3">
         <v>11</v>
@@ -4956,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="1">
         <v>0</v>
@@ -5061,18 +5061,18 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3">
         <v>10</v>
@@ -5192,18 +5192,18 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E35" s="3">
         <v>10</v>
@@ -5323,18 +5323,18 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E36" s="1">
         <v>10</v>
@@ -5454,18 +5454,18 @@
         <v>1.3900000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E37" s="1">
         <v>8</v>
@@ -5585,18 +5585,18 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E38" s="1">
         <v>8</v>
@@ -5716,18 +5716,18 @@
         <v>1.3800000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="1">
         <v>10.5</v>
@@ -5847,18 +5847,18 @@
         <v>1.6600000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40" s="1">
         <v>10</v>
@@ -5978,18 +5978,18 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E41" s="1">
         <v>16</v>
@@ -6109,18 +6109,18 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E42" s="1">
         <v>11</v>
@@ -6240,18 +6240,18 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E43" s="1">
         <v>11</v>
@@ -6371,18 +6371,18 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E44" s="1">
         <v>16</v>
@@ -6502,18 +6502,18 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" s="1">
         <v>10.5</v>
@@ -6633,18 +6633,18 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" s="1">
         <v>10</v>
@@ -6764,18 +6764,18 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47" s="1">
         <v>11</v>
@@ -6895,18 +6895,18 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E48" s="1">
         <v>13</v>
@@ -7026,18 +7026,18 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49" s="1">
         <v>12</v>
@@ -7157,18 +7157,18 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50" s="1">
         <v>10</v>
@@ -7288,18 +7288,18 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E51" s="1">
         <v>10</v>
@@ -7419,18 +7419,18 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E52" s="3">
         <v>7</v>
